--- a/public/exports-60-250-with-coowners/29189633.xlsx
+++ b/public/exports-60-250-with-coowners/29189633.xlsx
@@ -6289,12 +6289,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365263</t>
+          <t xml:space="preserve">311365262</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365266</t>
+          <t xml:space="preserve">311365267</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366605</t>
+          <t xml:space="preserve">311366603</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
